--- a/extraction_script/data/ابلاغ.xlsx
+++ b/extraction_script/data/ابلاغ.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting\extraction_script\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting1\extraction_script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C087C79-B05C-4A54-AA41-2AECA1920BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADD4433-FCCD-446C-AFB3-BF902E54B7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="16200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31380" yWindow="4695" windowWidth="15375" windowHeight="11505" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ابلاغ_1" sheetId="1" r:id="rId1"/>
-    <sheet name="ابلاغ_3" sheetId="2" r:id="rId2"/>
-    <sheet name="ابلاغ_4" sheetId="3" r:id="rId3"/>
-    <sheet name="ابلاغ_5" sheetId="4" r:id="rId4"/>
-    <sheet name="ابلاغ_2" sheetId="5" r:id="rId5"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="3" sheetId="2" r:id="rId2"/>
+    <sheet name="4" sheetId="3" r:id="rId3"/>
+    <sheet name="5" sheetId="4" r:id="rId4"/>
+    <sheet name="2" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
